--- a/data/Unusable_Links.xlsx
+++ b/data/Unusable_Links.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160DD694-EA31-4A75-B0FA-B4BAB5EF79D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EF9257-D6DC-4BEF-A09C-E1384033FEB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="174" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="254" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="alpha" sheetId="3" r:id="rId2"/>
-    <sheet name="SR" sheetId="2" r:id="rId3"/>
+    <sheet name="unusable" sheetId="1" r:id="rId1"/>
+    <sheet name="Pending" sheetId="4" r:id="rId2"/>
+    <sheet name="alpha" sheetId="3" r:id="rId3"/>
+    <sheet name="SR" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$270</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Pending!$A$2:$L$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">unusable!$A$1:$L$272</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2385" uniqueCount="1277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2686" uniqueCount="1334">
   <si>
     <t>link</t>
   </si>
@@ -3872,13 +3874,184 @@
   </si>
   <si>
     <t>1f-1f,enema</t>
+  </si>
+  <si>
+    <t>2f-1f</t>
+  </si>
+  <si>
+    <t>https://www.kink.com/shoot/13834</t>
+  </si>
+  <si>
+    <t>dakota skye</t>
+  </si>
+  <si>
+    <t>petite,small</t>
+  </si>
+  <si>
+    <t>https://bdsmstreak.com/video/93998/the-naive-model-and-the-creepy-photographer</t>
+  </si>
+  <si>
+    <t>https://www.kink.com/shoot/5843</t>
+  </si>
+  <si>
+    <t>kink men in pain</t>
+  </si>
+  <si>
+    <t>bdsm-hard-femdom</t>
+  </si>
+  <si>
+    <t>candence lux</t>
+  </si>
+  <si>
+    <t>https://bdsmstreak.com/video/93587/the-new-bitch</t>
+  </si>
+  <si>
+    <t>https://bdsmstreak.com/video/70025/the-new-bitch</t>
+  </si>
+  <si>
+    <t>mia bangg</t>
+  </si>
+  <si>
+    <t>spreader bar,sweaty</t>
+  </si>
+  <si>
+    <t>https://bdsmstreak.com/video/88715/sex-and-submission-the-night-nurse-dani-daniels</t>
+  </si>
+  <si>
+    <t>oiled,bent,nipple mouse traps</t>
+  </si>
+  <si>
+    <t>https://bdsmstreak.com/video/94000/the-return-of-darling</t>
+  </si>
+  <si>
+    <t>https://bdsmstreak.com/video/83324/bondage-the-sarge-meets-mia-bangg</t>
+  </si>
+  <si>
+    <t>submerged</t>
+  </si>
+  <si>
+    <t>https://heavyfetish.com/videos/12468/graias-the-terminator-the-groovy-and-the-faithful-slave-04/</t>
+  </si>
+  <si>
+    <t>graias</t>
+  </si>
+  <si>
+    <t>2f-1f1m</t>
+  </si>
+  <si>
+    <t>groovy,terminator,slave</t>
+  </si>
+  <si>
+    <t>harmony,rebecca blue</t>
+  </si>
+  <si>
+    <t>https://www.kink.com/shoot/6350</t>
+  </si>
+  <si>
+    <t>https://bdsmstreak.com/video/43566/tied-together-kate-kennedy-and-dolly-mattel</t>
+  </si>
+  <si>
+    <t>kate kenzie,dolly mattel</t>
+  </si>
+  <si>
+    <t>https://bdsmmansion.com/video/11463/latina-bound-to-wood-stake-and-fucked-jynx-maze/</t>
+  </si>
+  <si>
+    <t>jynx maze</t>
+  </si>
+  <si>
+    <t>https://bdsmstreak.com/video/25183/odette-delacroix</t>
+  </si>
+  <si>
+    <t>https://hcbdsm.com/video/107222/tiny-blonde-tied-up-and-ass-fucked-in-public2/</t>
+  </si>
+  <si>
+    <t>casey calvert,dee williams</t>
+  </si>
+  <si>
+    <t>2f-1m,inverted,pretzel</t>
+  </si>
+  <si>
+    <t>https://www.eporner.com/video-bBBbPvnEkFe/tiny-casey-calvert-is-inverted-skull-fucked-pussy/</t>
+  </si>
+  <si>
+    <t>isabella nice</t>
+  </si>
+  <si>
+    <t>https://bdsmstreak.com/video/70073/tiny-sex-kitten-isabella-nice-submits-in-rope-bondage-and-anal-fucking</t>
+  </si>
+  <si>
+    <t>bailey paige</t>
+  </si>
+  <si>
+    <t>https://www.twistedfactory.com/shoot/37110</t>
+  </si>
+  <si>
+    <t>pube pull</t>
+  </si>
+  <si>
+    <t>https://bdsmstreak.com/video/89701/tomi-knox-assaults-fuck-doll-kristine-kahill-with-creative-devices-and-sadism</t>
+  </si>
+  <si>
+    <t>kristine kahill</t>
+  </si>
+  <si>
+    <t>inverted,torch in pussy at 24m,anal hook pussy</t>
+  </si>
+  <si>
+    <t>https://bdsmstreak.com/video/76888/tough-as-nails</t>
+  </si>
+  <si>
+    <t>elise graves,donna dolore</t>
+  </si>
+  <si>
+    <t>https://www.kink.com/shoot/27059</t>
+  </si>
+  <si>
+    <t>https://bdsmstreak.com/video/76669/tough-as-nails-cassandra-nix</t>
+  </si>
+  <si>
+    <t>cassandra nix</t>
+  </si>
+  <si>
+    <t>wax,close pussy stick,anal hook</t>
+  </si>
+  <si>
+    <t>https://hcbdsm.com/video/110053/tough-blonde-bombshell-fan-favorite-lorelei-lee-complete-edited-live-show3/</t>
+  </si>
+  <si>
+    <t>https://bdsmstreak.com/video/81358/tracey-sweet</t>
+  </si>
+  <si>
+    <t>riley james, lea lexis</t>
+  </si>
+  <si>
+    <t>https://bdsmstreak.com/video/72136/two-cunts-one-game</t>
+  </si>
+  <si>
+    <t>jade indica,donna dolore,ariel x</t>
+  </si>
+  <si>
+    <t>https://www.kink.com/shoot/7102</t>
+  </si>
+  <si>
+    <t>120,pd</t>
+  </si>
+  <si>
+    <t>insex</t>
+  </si>
+  <si>
+    <t>from main list for duplicate check</t>
+  </si>
+  <si>
+    <t>These records stayed pending</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3929,6 +4102,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -3954,7 +4134,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -3992,13 +4172,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4019,15 +4212,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4035,7 +4236,47 @@
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4141,15 +4382,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE68EB38-645C-40D9-BED9-2A11831302E7}" name="Table1" displayName="Table1" ref="A1:C26" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE68EB38-645C-40D9-BED9-2A11831302E7}" name="Table1" displayName="Table1" ref="A1:C26" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <autoFilter ref="A1:C26" xr:uid="{BE68EB38-645C-40D9-BED9-2A11831302E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B26">
     <sortCondition ref="B1:B26"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E2B5FC3E-0281-4EE0-AB45-F0D82FAF49B6}" name="letter" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{05E7DFA0-3FA3-4813-A227-017A6D141AE8}" name="frequency" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{A0B2B540-48FA-4BE3-ABBF-44BC64E7DE4C}" name="Column1" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{E2B5FC3E-0281-4EE0-AB45-F0D82FAF49B6}" name="letter" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{05E7DFA0-3FA3-4813-A227-017A6D141AE8}" name="frequency" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{A0B2B540-48FA-4BE3-ABBF-44BC64E7DE4C}" name="Column1" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4418,7 +4659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N270"/>
+  <dimension ref="A1:N272"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="43" style="1" customWidth="1"/>
@@ -4432,8 +4673,8 @@
     <col min="10" max="10" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.85546875" style="1" customWidth="1"/>
     <col min="12" max="12" width="11.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" style="1" customWidth="1"/>
+    <col min="14" max="14" width="6.5703125" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -4475,12 +4716,12 @@
         <v>715</v>
       </c>
       <c r="M1" s="3">
-        <f>COUNTIF(J2:J996,"done")</f>
-        <v>225</v>
+        <f>COUNTIF(J2:J998,"done")</f>
+        <v>248</v>
       </c>
       <c r="N1" s="4">
-        <f>COUNTIF(J2:J996,"pending")</f>
-        <v>44</v>
+        <f>COUNTIF(J2:J998,"pending")</f>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="45" x14ac:dyDescent="0.25">
@@ -9453,14 +9694,14 @@
       <c r="C126" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D126" s="2" t="s">
-        <v>16</v>
+      <c r="D126" s="2">
+        <v>75</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>16</v>
+        <v>1331</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>16</v>
+        <v>1330</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>15</v>
@@ -12083,7 +12324,7 @@
         <v>p</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>458</v>
       </c>
@@ -12192,14 +12433,14 @@
         <v>1204</v>
       </c>
       <c r="J194" s="2" t="str">
-        <f t="shared" ref="J194:J257" si="6">IF(C194&lt;&gt;"-","done","pending")</f>
+        <f t="shared" ref="J194:J259" si="6">IF(C194&lt;&gt;"-","done","pending")</f>
         <v>pending</v>
       </c>
       <c r="K194" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L194" s="2" t="str">
-        <f t="shared" ref="L194:L257" si="7">LEFT(B194,1)</f>
+        <f t="shared" ref="L194:L259" si="7">LEFT(B194,1)</f>
         <v>p</v>
       </c>
     </row>
@@ -12243,7 +12484,7 @@
         <v>p</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>466</v>
       </c>
@@ -12403,7 +12644,7 @@
         <v>p</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>474</v>
       </c>
@@ -13363,7 +13604,7 @@
         <v>s</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>516</v>
       </c>
@@ -13523,7 +13764,7 @@
         <v>s</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>524</v>
       </c>
@@ -13563,7 +13804,7 @@
         <v>s</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>526</v>
       </c>
@@ -13603,7 +13844,7 @@
         <v>s</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>528</v>
       </c>
@@ -13931,7 +14172,7 @@
         <v>547</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>16</v>
+        <v>1278</v>
       </c>
       <c r="D238" s="2">
         <v>52</v>
@@ -13949,11 +14190,11 @@
         <v>0</v>
       </c>
       <c r="I238" s="2" t="s">
-        <v>16</v>
+        <v>1277</v>
       </c>
       <c r="J238" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K238" s="2" t="b">
         <v>0</v>
@@ -13963,7 +14204,7 @@
         <v>t</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>548</v>
       </c>
@@ -13971,17 +14212,29 @@
         <v>549</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D239" s="2"/>
-      <c r="E239" s="2"/>
-      <c r="F239" s="2"/>
-      <c r="G239" s="2"/>
-      <c r="H239" s="2"/>
-      <c r="I239" s="2"/>
+        <v>1281</v>
+      </c>
+      <c r="D239" s="2">
+        <v>70</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="G239" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H239" s="2">
+        <v>1</v>
+      </c>
+      <c r="I239" s="2" t="s">
+        <v>1280</v>
+      </c>
       <c r="J239" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K239" s="2" t="b">
         <v>0</v>
@@ -13991,53 +14244,77 @@
         <v>t</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>550</v>
+        <v>1282</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>551</v>
+        <v>1282</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D240" s="2"/>
-      <c r="E240" s="2"/>
-      <c r="F240" s="2"/>
-      <c r="G240" s="2"/>
-      <c r="H240" s="2"/>
-      <c r="I240" s="2"/>
+        <v>1286</v>
+      </c>
+      <c r="D240" s="2">
+        <v>34</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="H240" s="2">
+        <v>0</v>
+      </c>
+      <c r="I240" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="J240" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>pending</v>
+        <f t="shared" ref="J240" si="8">IF(C240&lt;&gt;"-","done","pending")</f>
+        <v>done</v>
       </c>
       <c r="K240" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L240" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>t</v>
+        <f t="shared" ref="L240" si="9">LEFT(B240,1)</f>
+        <v>h</v>
       </c>
     </row>
     <row r="241" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D241" s="2"/>
-      <c r="E241" s="2"/>
-      <c r="F241" s="2"/>
-      <c r="G241" s="2"/>
-      <c r="H241" s="2"/>
-      <c r="I241" s="2"/>
+        <v>1287</v>
+      </c>
+      <c r="D241" s="2">
+        <v>48</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G241" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H241" s="2">
+        <v>2</v>
+      </c>
+      <c r="I241" s="2" t="s">
+        <v>690</v>
+      </c>
       <c r="J241" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K241" s="2" t="b">
         <v>0</v>
@@ -14047,25 +14324,37 @@
         <v>t</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D242" s="2"/>
-      <c r="E242" s="2"/>
-      <c r="F242" s="2"/>
-      <c r="G242" s="2"/>
-      <c r="H242" s="2"/>
-      <c r="I242" s="2"/>
+        <v>1290</v>
+      </c>
+      <c r="D242" s="2">
+        <v>57</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="G242" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H242" s="2">
+        <v>4</v>
+      </c>
+      <c r="I242" s="2" t="s">
+        <v>1289</v>
+      </c>
       <c r="J242" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K242" s="2" t="b">
         <v>0</v>
@@ -14077,23 +14366,35 @@
     </row>
     <row r="243" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D243" s="2"/>
-      <c r="E243" s="2"/>
-      <c r="F243" s="2"/>
-      <c r="G243" s="2"/>
-      <c r="H243" s="2"/>
-      <c r="I243" s="2"/>
+        <v>1292</v>
+      </c>
+      <c r="D243" s="2">
+        <v>62</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="G243" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H243" s="2">
+        <v>8</v>
+      </c>
+      <c r="I243" s="2" t="s">
+        <v>1291</v>
+      </c>
       <c r="J243" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K243" s="2" t="b">
         <v>0</v>
@@ -14105,23 +14406,35 @@
     </row>
     <row r="244" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D244" s="2"/>
-      <c r="E244" s="2"/>
-      <c r="F244" s="2"/>
-      <c r="G244" s="2"/>
-      <c r="H244" s="2"/>
-      <c r="I244" s="2"/>
+        <v>1293</v>
+      </c>
+      <c r="D244" s="2">
+        <v>52</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G244" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H244" s="2">
+        <v>3</v>
+      </c>
+      <c r="I244" s="2" t="s">
+        <v>1294</v>
+      </c>
       <c r="J244" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K244" s="2" t="b">
         <v>0</v>
@@ -14131,25 +14444,37 @@
         <v>t</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D245" s="2"/>
-      <c r="E245" s="2"/>
-      <c r="F245" s="2"/>
-      <c r="G245" s="2"/>
-      <c r="H245" s="2"/>
-      <c r="I245" s="2"/>
+        <v>1295</v>
+      </c>
+      <c r="D245" s="2">
+        <v>41</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G245" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H245" s="2">
+        <v>0</v>
+      </c>
+      <c r="I245" s="2" t="s">
+        <v>1297</v>
+      </c>
       <c r="J245" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K245" s="2" t="b">
         <v>0</v>
@@ -14159,25 +14484,37 @@
         <v>t</v>
       </c>
     </row>
-    <row r="246" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D246" s="2"/>
-      <c r="E246" s="2"/>
-      <c r="F246" s="2"/>
-      <c r="G246" s="2"/>
-      <c r="H246" s="2"/>
-      <c r="I246" s="2"/>
+        <v>1300</v>
+      </c>
+      <c r="D246" s="2">
+        <v>44</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G246" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H246" s="2">
+        <v>0</v>
+      </c>
+      <c r="I246" s="2" t="s">
+        <v>1262</v>
+      </c>
       <c r="J246" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K246" s="2" t="b">
         <v>0</v>
@@ -14189,23 +14526,35 @@
     </row>
     <row r="247" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D247" s="2"/>
-      <c r="E247" s="2"/>
-      <c r="F247" s="2"/>
-      <c r="G247" s="2"/>
-      <c r="H247" s="2"/>
-      <c r="I247" s="2"/>
+        <v>1301</v>
+      </c>
+      <c r="D247" s="2">
+        <v>40</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="F247" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="G247" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H247" s="2">
+        <v>0</v>
+      </c>
+      <c r="I247" s="2" t="s">
+        <v>941</v>
+      </c>
       <c r="J247" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K247" s="2" t="b">
         <v>0</v>
@@ -14217,23 +14566,35 @@
     </row>
     <row r="248" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D248" s="2"/>
-      <c r="E248" s="2"/>
-      <c r="F248" s="2"/>
-      <c r="G248" s="2"/>
-      <c r="H248" s="2"/>
-      <c r="I248" s="2"/>
+        <v>1303</v>
+      </c>
+      <c r="D248" s="2">
+        <v>27</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G248" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H248" s="2">
+        <v>0</v>
+      </c>
+      <c r="I248" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="J248" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K248" s="2" t="b">
         <v>0</v>
@@ -14243,25 +14604,37 @@
         <v>t</v>
       </c>
     </row>
-    <row r="249" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D249" s="2"/>
-      <c r="E249" s="2"/>
-      <c r="F249" s="2"/>
-      <c r="G249" s="2"/>
-      <c r="H249" s="2"/>
-      <c r="I249" s="2"/>
+        <v>1305</v>
+      </c>
+      <c r="D249" s="2">
+        <v>19</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="G249" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H249" s="2">
+        <v>0</v>
+      </c>
+      <c r="I249" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="J249" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K249" s="2" t="b">
         <v>0</v>
@@ -14271,25 +14644,37 @@
         <v>t</v>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D250" s="2"/>
-      <c r="E250" s="2"/>
-      <c r="F250" s="2"/>
-      <c r="G250" s="2"/>
-      <c r="H250" s="2"/>
-      <c r="I250" s="2"/>
+        <v>1306</v>
+      </c>
+      <c r="D250" s="2">
+        <v>67</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="G250" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H250" s="2">
+        <v>0</v>
+      </c>
+      <c r="I250" s="2" t="s">
+        <v>1215</v>
+      </c>
       <c r="J250" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K250" s="2" t="b">
         <v>0</v>
@@ -14301,23 +14686,35 @@
     </row>
     <row r="251" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D251" s="2"/>
-      <c r="E251" s="2"/>
-      <c r="F251" s="2"/>
-      <c r="G251" s="2"/>
-      <c r="H251" s="2"/>
-      <c r="I251" s="2"/>
+        <v>1309</v>
+      </c>
+      <c r="D251" s="2">
+        <v>23</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="F251" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G251" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H251" s="2">
+        <v>0</v>
+      </c>
+      <c r="I251" s="2" t="s">
+        <v>1308</v>
+      </c>
       <c r="J251" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K251" s="2" t="b">
         <v>0</v>
@@ -14327,25 +14724,37 @@
         <v>t</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D252" s="2"/>
-      <c r="E252" s="2"/>
-      <c r="F252" s="2"/>
-      <c r="G252" s="2"/>
-      <c r="H252" s="2"/>
-      <c r="I252" s="2"/>
+        <v>1311</v>
+      </c>
+      <c r="D252" s="2">
+        <v>50</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="F252" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="G252" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H252" s="2">
+        <v>0</v>
+      </c>
+      <c r="I252" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="J252" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K252" s="2" t="b">
         <v>0</v>
@@ -14355,25 +14764,37 @@
         <v>t</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D253" s="2"/>
-      <c r="E253" s="2"/>
-      <c r="F253" s="2"/>
-      <c r="G253" s="2"/>
-      <c r="H253" s="2"/>
-      <c r="I253" s="2"/>
+        <v>1313</v>
+      </c>
+      <c r="D253" s="2">
+        <v>63</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G253" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H253" s="2">
+        <v>2</v>
+      </c>
+      <c r="I253" s="2" t="s">
+        <v>1314</v>
+      </c>
       <c r="J253" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K253" s="2" t="b">
         <v>0</v>
@@ -14383,25 +14804,37 @@
         <v>t</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D254" s="2"/>
-      <c r="E254" s="2"/>
-      <c r="F254" s="2"/>
-      <c r="G254" s="2"/>
-      <c r="H254" s="2"/>
-      <c r="I254" s="2"/>
+        <v>1315</v>
+      </c>
+      <c r="D254" s="2">
+        <v>42</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F254" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G254" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H254" s="2">
+        <v>6</v>
+      </c>
+      <c r="I254" s="2" t="s">
+        <v>1317</v>
+      </c>
       <c r="J254" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K254" s="2" t="b">
         <v>0</v>
@@ -14411,25 +14844,37 @@
         <v>t</v>
       </c>
     </row>
-    <row r="255" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D255" s="2"/>
-      <c r="E255" s="2"/>
-      <c r="F255" s="2"/>
-      <c r="G255" s="2"/>
-      <c r="H255" s="2"/>
-      <c r="I255" s="2"/>
+        <v>1318</v>
+      </c>
+      <c r="D255" s="2">
+        <v>63</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F255" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G255" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H255" s="2">
+        <v>0</v>
+      </c>
+      <c r="I255" s="2" t="s">
+        <v>1262</v>
+      </c>
       <c r="J255" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K255" s="2" t="b">
         <v>0</v>
@@ -14439,53 +14884,77 @@
         <v>t</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>582</v>
+        <v>1320</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>583</v>
+        <v>1321</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D256" s="2"/>
-      <c r="E256" s="2"/>
-      <c r="F256" s="2"/>
-      <c r="G256" s="2"/>
-      <c r="H256" s="2"/>
-      <c r="I256" s="2"/>
+        <v>1321</v>
+      </c>
+      <c r="D256" s="2">
+        <v>61</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F256" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G256" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H256" s="2">
+        <v>2</v>
+      </c>
+      <c r="I256" s="2" t="s">
+        <v>1323</v>
+      </c>
       <c r="J256" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v>pending</v>
+        <f t="shared" ref="J256" si="10">IF(C256&lt;&gt;"-","done","pending")</f>
+        <v>done</v>
       </c>
       <c r="K256" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L256" s="2" t="str">
-        <f t="shared" si="7"/>
-        <v>t</v>
-      </c>
-    </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+        <f t="shared" ref="L256" si="11">LEFT(B256,1)</f>
+        <v>h</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D257" s="2"/>
-      <c r="E257" s="2"/>
-      <c r="F257" s="2"/>
-      <c r="G257" s="2"/>
-      <c r="H257" s="2"/>
-      <c r="I257" s="2"/>
+        <v>1324</v>
+      </c>
+      <c r="D257" s="2">
+        <v>90</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="G257" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H257" s="2">
+        <v>0</v>
+      </c>
+      <c r="I257" s="2" t="s">
+        <v>787</v>
+      </c>
       <c r="J257" s="2" t="str">
         <f t="shared" si="6"/>
-        <v>pending</v>
+        <v>done</v>
       </c>
       <c r="K257" s="2" t="b">
         <v>0</v>
@@ -14497,486 +14966,596 @@
     </row>
     <row r="258" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D258" s="2"/>
-      <c r="E258" s="2"/>
-      <c r="F258" s="2"/>
-      <c r="G258" s="2"/>
-      <c r="H258" s="2"/>
-      <c r="I258" s="2"/>
+        <v>1325</v>
+      </c>
+      <c r="D258" s="2">
+        <v>66</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F258" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="G258" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H258" s="2">
+        <v>0</v>
+      </c>
+      <c r="I258" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="J258" s="2" t="str">
-        <f t="shared" ref="J258:J270" si="8">IF(C258&lt;&gt;"-","done","pending")</f>
-        <v>pending</v>
+        <f t="shared" si="6"/>
+        <v>done</v>
       </c>
       <c r="K258" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L258" s="2" t="str">
-        <f t="shared" ref="L258:L270" si="9">LEFT(B258,1)</f>
+        <f t="shared" si="7"/>
         <v>t</v>
       </c>
     </row>
-    <row r="259" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D259" s="2"/>
-      <c r="E259" s="2"/>
-      <c r="F259" s="2"/>
-      <c r="G259" s="2"/>
-      <c r="H259" s="2"/>
-      <c r="I259" s="2"/>
+        <v>1327</v>
+      </c>
+      <c r="D259" s="2">
+        <v>61</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G259" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H259" s="2">
+        <v>0</v>
+      </c>
+      <c r="I259" s="2" t="s">
+        <v>1262</v>
+      </c>
       <c r="J259" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>pending</v>
+        <f t="shared" si="6"/>
+        <v>done</v>
       </c>
       <c r="K259" s="2" t="b">
         <v>0</v>
       </c>
       <c r="L259" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>t</v>
       </c>
     </row>
     <row r="260" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G260" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H260" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I260" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J260" s="2" t="str">
+        <f t="shared" ref="J260:J272" si="12">IF(C260&lt;&gt;"-","done","pending")</f>
+        <v>pending</v>
+      </c>
+      <c r="K260" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L260" s="2" t="str">
+        <f t="shared" ref="L260:L272" si="13">LEFT(B260,1)</f>
+        <v>t</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A261" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D261" s="2">
+        <v>77</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F261" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G261" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H261" s="2">
+        <v>0</v>
+      </c>
+      <c r="I261" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J261" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v>done</v>
+      </c>
+      <c r="K261" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L261" s="2" t="str">
+        <f t="shared" si="13"/>
+        <v>t</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="B260" s="2" t="s">
+      <c r="B262" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="C260" s="2" t="s">
+      <c r="C262" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="D260" s="2">
+      <c r="D262" s="2">
         <v>44</v>
       </c>
-      <c r="E260" s="2" t="s">
+      <c r="E262" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F260" s="2" t="s">
+      <c r="F262" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="G260" s="2" t="s">
+      <c r="G262" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H260" s="2">
-        <v>0</v>
-      </c>
-      <c r="I260" s="2" t="s">
+      <c r="H262" s="2">
+        <v>0</v>
+      </c>
+      <c r="I262" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="J260" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>done</v>
-      </c>
-      <c r="K260" s="2" t="b">
+      <c r="J262" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v>done</v>
+      </c>
+      <c r="K262" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="L260" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>v</v>
-      </c>
-    </row>
-    <row r="261" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A261" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="D261" s="2">
-        <v>59</v>
-      </c>
-      <c r="E261" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="F261" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="G261" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H261" s="2">
-        <v>8</v>
-      </c>
-      <c r="I261" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="J261" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>done</v>
-      </c>
-      <c r="K261" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L261" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>v</v>
-      </c>
-    </row>
-    <row r="262" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A262" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="D262" s="2">
-        <v>67</v>
-      </c>
-      <c r="E262" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="F262" s="2" t="s">
-        <v>893</v>
-      </c>
-      <c r="G262" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H262" s="2">
-        <v>0</v>
-      </c>
-      <c r="I262" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J262" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>done</v>
-      </c>
-      <c r="K262" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="L262" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>v</v>
       </c>
     </row>
     <row r="263" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>1171</v>
+        <v>891</v>
       </c>
       <c r="D263" s="2">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>20</v>
+        <v>658</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>708</v>
+        <v>890</v>
       </c>
       <c r="G263" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H263" s="2">
+        <v>8</v>
+      </c>
+      <c r="I263" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="J263" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v>done</v>
+      </c>
+      <c r="K263" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L263" s="2" t="str">
+        <f t="shared" si="13"/>
+        <v>v</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A264" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="D264" s="2">
+        <v>67</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="F264" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="G264" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H264" s="2">
+        <v>0</v>
+      </c>
+      <c r="I264" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J264" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v>done</v>
+      </c>
+      <c r="K264" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L264" s="2" t="str">
+        <f t="shared" si="13"/>
+        <v>v</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A265" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D265" s="2">
+        <v>63</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F265" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="G265" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H265" s="2">
         <v>3</v>
       </c>
-      <c r="I263" s="2" t="s">
+      <c r="I265" s="2" t="s">
         <v>1170</v>
       </c>
-      <c r="J263" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>done</v>
-      </c>
-      <c r="K263" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L263" s="2" t="str">
-        <f t="shared" si="9"/>
+      <c r="J265" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v>done</v>
+      </c>
+      <c r="K265" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L265" s="2" t="str">
+        <f t="shared" si="13"/>
         <v>w</v>
       </c>
     </row>
-    <row r="264" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A264" s="2" t="s">
+    <row r="266" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A266" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="B264" s="2" t="s">
+      <c r="B266" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="C264" s="2" t="s">
+      <c r="C266" s="2" t="s">
         <v>1173</v>
       </c>
-      <c r="D264" s="2">
+      <c r="D266" s="2">
         <v>44</v>
       </c>
-      <c r="E264" s="2" t="s">
+      <c r="E266" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F264" s="2" t="s">
+      <c r="F266" s="2" t="s">
         <v>1172</v>
       </c>
-      <c r="G264" s="2" t="s">
+      <c r="G266" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H264" s="2">
-        <v>0</v>
-      </c>
-      <c r="I264" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J264" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>done</v>
-      </c>
-      <c r="K264" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L264" s="2" t="str">
-        <f t="shared" si="9"/>
+      <c r="H266" s="2">
+        <v>0</v>
+      </c>
+      <c r="I266" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J266" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v>done</v>
+      </c>
+      <c r="K266" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L266" s="2" t="str">
+        <f t="shared" si="13"/>
         <v>w</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A265" s="2" t="s">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A267" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="B265" s="2" t="s">
+      <c r="B267" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="C265" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D265" s="2"/>
-      <c r="E265" s="2"/>
-      <c r="F265" s="2"/>
-      <c r="G265" s="2"/>
-      <c r="H265" s="2"/>
-      <c r="I265" s="2"/>
-      <c r="J265" s="2" t="str">
-        <f t="shared" si="8"/>
+      <c r="C267" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D267" s="2"/>
+      <c r="E267" s="2"/>
+      <c r="F267" s="2"/>
+      <c r="G267" s="2"/>
+      <c r="H267" s="2"/>
+      <c r="I267" s="2"/>
+      <c r="J267" s="2" t="str">
+        <f t="shared" si="12"/>
         <v>pending</v>
       </c>
-      <c r="K265" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L265" s="2" t="str">
-        <f t="shared" si="9"/>
+      <c r="K267" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L267" s="2" t="str">
+        <f t="shared" si="13"/>
         <v>w</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A266" s="2" t="s">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A268" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="B266" s="2" t="s">
+      <c r="B268" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="C266" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D266" s="2"/>
-      <c r="E266" s="2"/>
-      <c r="F266" s="2"/>
-      <c r="G266" s="2"/>
-      <c r="H266" s="2"/>
-      <c r="I266" s="2"/>
-      <c r="J266" s="2" t="str">
-        <f t="shared" si="8"/>
+      <c r="C268" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D268" s="2"/>
+      <c r="E268" s="2"/>
+      <c r="F268" s="2"/>
+      <c r="G268" s="2"/>
+      <c r="H268" s="2"/>
+      <c r="I268" s="2"/>
+      <c r="J268" s="2" t="str">
+        <f t="shared" si="12"/>
         <v>pending</v>
       </c>
-      <c r="K266" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L266" s="2" t="str">
-        <f t="shared" si="9"/>
+      <c r="K268" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L268" s="2" t="str">
+        <f t="shared" si="13"/>
         <v>w</v>
       </c>
     </row>
-    <row r="267" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A267" s="2" t="s">
+    <row r="269" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A269" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="B267" s="2" t="s">
+      <c r="B269" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="C267" s="2" t="s">
+      <c r="C269" s="2" t="s">
         <v>1175</v>
       </c>
-      <c r="D267" s="2">
+      <c r="D269" s="2">
         <v>61</v>
       </c>
-      <c r="E267" s="2" t="s">
+      <c r="E269" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F267" s="2" t="s">
+      <c r="F269" s="2" t="s">
         <v>1174</v>
       </c>
-      <c r="G267" s="2" t="s">
+      <c r="G269" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H267" s="2">
+      <c r="H269" s="2">
         <v>5</v>
       </c>
-      <c r="I267" s="2" t="s">
+      <c r="I269" s="2" t="s">
         <v>910</v>
       </c>
-      <c r="J267" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>done</v>
-      </c>
-      <c r="K267" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L267" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>w</v>
-      </c>
-    </row>
-    <row r="268" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A268" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>1176</v>
-      </c>
-      <c r="D268" s="2">
-        <v>69</v>
-      </c>
-      <c r="E268" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="F268" s="2" t="s">
-        <v>1172</v>
-      </c>
-      <c r="G268" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H268" s="2">
-        <v>0</v>
-      </c>
-      <c r="I268" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J268" s="2" t="str">
-        <f t="shared" si="8"/>
-        <v>done</v>
-      </c>
-      <c r="K268" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L268" s="2" t="str">
-        <f t="shared" si="9"/>
-        <v>w</v>
-      </c>
-    </row>
-    <row r="269" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A269" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D269" s="2">
-        <v>49</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F269" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G269" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H269" s="2">
-        <v>4</v>
-      </c>
-      <c r="I269" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="J269" s="2" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>done</v>
       </c>
       <c r="K269" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L269" s="2" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v>w</v>
       </c>
     </row>
     <row r="270" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D270" s="2">
+        <v>69</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="F270" s="2" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G270" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H270" s="2">
+        <v>0</v>
+      </c>
+      <c r="I270" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J270" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v>done</v>
+      </c>
+      <c r="K270" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L270" s="2" t="str">
+        <f t="shared" si="13"/>
+        <v>w</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D271" s="2">
+        <v>49</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F271" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G271" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H271" s="2">
+        <v>4</v>
+      </c>
+      <c r="I271" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J271" s="2" t="str">
+        <f t="shared" si="12"/>
+        <v>done</v>
+      </c>
+      <c r="K271" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L271" s="2" t="str">
+        <f t="shared" si="13"/>
+        <v>w</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A272" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="B270" s="2" t="s">
+      <c r="B272" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="C270" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D270" s="2">
+      <c r="C272" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D272" s="2">
         <v>86</v>
       </c>
-      <c r="E270" s="2" t="s">
+      <c r="E272" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F270" s="2" t="s">
+      <c r="F272" s="2" t="s">
         <v>1177</v>
       </c>
-      <c r="G270" s="2" t="s">
+      <c r="G272" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H270" s="2">
+      <c r="H272" s="2">
         <v>6</v>
       </c>
-      <c r="I270" s="2" t="s">
+      <c r="I272" s="2" t="s">
         <v>1178</v>
       </c>
-      <c r="J270" s="2" t="str">
-        <f t="shared" si="8"/>
+      <c r="J272" s="2" t="str">
+        <f t="shared" si="12"/>
         <v>pending</v>
       </c>
-      <c r="K270" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L270" s="2" t="str">
-        <f t="shared" si="9"/>
+      <c r="K272" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L272" s="2" t="str">
+        <f t="shared" si="13"/>
         <v>w</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L270" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N270">
-    <sortCondition ref="L1:L270"/>
+  <autoFilter ref="A1:L272" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N272">
+    <sortCondition ref="L1:L272"/>
   </sortState>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+  <conditionalFormatting sqref="B240">
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C239 C241:C1048576">
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C240">
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="C102" r:id="rId1" xr:uid="{A724224A-E7CE-4FBD-8B88-9BDE47AD6632}"/>
@@ -14986,290 +15565,1270 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B477D216-E618-462F-AB65-6529362C57E1}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="3" width="40.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.28515625" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+    </row>
+    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="2" t="str">
+        <f t="shared" ref="J3:J25" si="0">IF(C3&lt;&gt;"-","done","pending")</f>
+        <v>pending</v>
+      </c>
+      <c r="K3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="str">
+        <f t="shared" ref="L3:L25" si="1">LEFT(B3,1)</f>
+        <v>a</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>a</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>a</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>a</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>a</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>b</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>b</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="2">
+        <v>75</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="2">
+        <v>7</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="J10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>i</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>i</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>j</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>l</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>p</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>p</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="2">
+        <v>71</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="2">
+        <v>5</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J16" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>p</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="2">
+        <v>15</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>r</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>r</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>r</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>r</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>s</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>t</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>w</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>w</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="2">
+        <v>86</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="2">
+        <v>6</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="J25" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>pending</v>
+      </c>
+      <c r="K25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>w</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:L25" xr:uid="{B477D216-E618-462F-AB65-6529362C57E1}"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A2:A25">
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C25">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC2DDC13-0A9A-46E4-A9CB-AB9518EAAEA3}">
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" style="11" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="1" width="8.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" style="9" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1157</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1158</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>1160</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>1133</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="9">
         <v>1</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="9" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>1134</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="9">
         <v>1</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="9" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="9" t="s">
         <v>1151</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="9">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="9" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="9" t="s">
         <v>1141</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="9">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="9" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="9" t="s">
         <v>1139</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="9">
         <v>3</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="9" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="9" t="s">
         <v>1143</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="9">
         <v>3</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="9" t="s">
         <v>1161</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="9" t="s">
         <v>1155</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <v>3</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="9" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="9" t="s">
         <v>1132</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="9">
         <v>4</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="9" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="9" t="s">
         <v>1142</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="9">
         <v>6</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="9" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>1145</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="9">
         <v>6</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="9" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="9" t="s">
         <v>1149</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="9">
         <v>6</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="9" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="9" t="s">
         <v>1148</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="9">
         <v>7</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="9" t="s">
         <v>1161</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="9" t="s">
         <v>1144</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="9">
         <v>8</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="9" t="s">
         <v>1161</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="9" t="s">
         <v>1152</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="9">
         <v>8</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="9" t="s">
         <v>1161</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="9" t="s">
         <v>1156</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="9">
         <v>9</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="9" t="s">
         <v>1161</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="9" t="s">
         <v>1146</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="9">
         <v>12</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="9" t="s">
         <v>1161</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="9" t="s">
         <v>1138</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="9">
         <v>13</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="9" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="9" t="s">
         <v>1140</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="9">
         <v>14</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="9" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="9" t="s">
         <v>1147</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="9">
         <v>14</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="9" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="9" t="s">
         <v>1137</v>
       </c>
-      <c r="B21" s="11">
-        <v>16</v>
-      </c>
-      <c r="C21" s="11" t="s">
+      <c r="B21" s="9">
+        <v>16</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>1159</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="9" t="s">
         <v>1150</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="9">
         <v>19</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="9" t="s">
         <v>1161</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="9" t="s">
         <v>1153</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="9">
         <v>22</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="9" t="s">
         <v>1161</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="9" t="s">
         <v>1136</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="9">
         <v>25</v>
       </c>
+      <c r="C24" s="9" t="s">
+        <v>1161</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="9" t="s">
         <v>1154</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="9">
         <v>29</v>
       </c>
+      <c r="C25" s="9" t="s">
+        <v>1161</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="9" t="s">
         <v>1135</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="9">
         <v>39</v>
       </c>
     </row>
@@ -15281,7 +16840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DAE8507-2DA5-4082-A77E-8DA3646B3110}">
   <dimension ref="A1:C385"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -15295,10 +16854,10 @@
       <c r="A1" s="5" t="s">
         <v>965</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="10" t="s">
         <v>1119</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="12" t="s">
         <v>1122</v>
       </c>
     </row>
@@ -15306,10 +16865,10 @@
       <c r="A2" s="6" t="s">
         <v>966</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>1077</v>
       </c>
-      <c r="C2" s="7" t="str">
+      <c r="C2" s="13" t="str">
         <f>LOWER(B2)</f>
         <v>slut interrogation</v>
       </c>
@@ -15318,10 +16877,10 @@
       <c r="A3" s="6" t="s">
         <v>967</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="11" t="s">
         <v>1078</v>
       </c>
-      <c r="C3" s="7" t="str">
+      <c r="C3" s="13" t="str">
         <f t="shared" ref="C3:C66" si="0">LOWER(B3)</f>
         <v>warning! extreme torment and mind bending orgasms</v>
       </c>
@@ -15330,10 +16889,10 @@
       <c r="A4" s="6" t="s">
         <v>968</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="11" t="s">
         <v>1079</v>
       </c>
-      <c r="C4" s="7" t="str">
+      <c r="C4" s="13" t="str">
         <f t="shared" si="0"/>
         <v>tall blond bombshell taken down</v>
       </c>
@@ -15342,10 +16901,10 @@
       <c r="A5" s="6" t="s">
         <v>969</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="11" t="s">
         <v>1080</v>
       </c>
-      <c r="C5" s="7" t="str">
+      <c r="C5" s="13" t="str">
         <f t="shared" si="0"/>
         <v>total domination</v>
       </c>
@@ -15354,10 +16913,10 @@
       <c r="A6" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="11" t="s">
         <v>1081</v>
       </c>
-      <c r="C6" s="7" t="str">
+      <c r="C6" s="13" t="str">
         <f t="shared" si="0"/>
         <v>please, mister, no</v>
       </c>
@@ -15366,10 +16925,10 @@
       <c r="A7" s="6" t="s">
         <v>971</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="11" t="s">
         <v>1082</v>
       </c>
-      <c r="C7" s="7" t="str">
+      <c r="C7" s="13" t="str">
         <f t="shared" si="0"/>
         <v>hardcore suffering and brutal orgasms</v>
       </c>
@@ -15378,10 +16937,10 @@
       <c r="A8" s="6" t="s">
         <v>972</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="11" t="s">
         <v>1083</v>
       </c>
-      <c r="C8" s="7" t="str">
+      <c r="C8" s="13" t="str">
         <f t="shared" si="0"/>
         <v>helpless whore's suffering</v>
       </c>
@@ -15390,10 +16949,10 @@
       <c r="A9" s="6" t="s">
         <v>973</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="11" t="s">
         <v>1084</v>
       </c>
-      <c r="C9" s="7" t="str">
+      <c r="C9" s="13" t="str">
         <f t="shared" si="0"/>
         <v>the destruction of cherry torn</v>
       </c>
@@ -15402,10 +16961,10 @@
       <c r="A10" s="6" t="s">
         <v>974</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="11" t="s">
         <v>1085</v>
       </c>
-      <c r="C10" s="7" t="str">
+      <c r="C10" s="13" t="str">
         <f t="shared" si="0"/>
         <v>reigning chaos on krysta</v>
       </c>
@@ -15414,10 +16973,10 @@
       <c r="A11" s="6" t="s">
         <v>975</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="11" t="s">
         <v>1086</v>
       </c>
-      <c r="C11" s="7" t="str">
+      <c r="C11" s="13" t="str">
         <f t="shared" si="0"/>
         <v>relentless brutality</v>
       </c>
@@ -15426,10 +16985,10 @@
       <c r="A12" s="6" t="s">
         <v>976</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="11" t="s">
         <v>1087</v>
       </c>
-      <c r="C12" s="7" t="str">
+      <c r="C12" s="13" t="str">
         <f t="shared" si="0"/>
         <v>taking a piece of pi</v>
       </c>
@@ -15438,10 +16997,10 @@
       <c r="A13" s="6" t="s">
         <v>977</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="11" t="s">
         <v>1088</v>
       </c>
-      <c r="C13" s="7" t="str">
+      <c r="C13" s="13" t="str">
         <f t="shared" si="0"/>
         <v>filthy whore</v>
       </c>
@@ -15450,10 +17009,10 @@
       <c r="A14" s="6" t="s">
         <v>978</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="11" t="s">
         <v>1089</v>
       </c>
-      <c r="C14" s="7" t="str">
+      <c r="C14" s="13" t="str">
         <f t="shared" si="0"/>
         <v>brutality and torment</v>
       </c>
@@ -15462,10 +17021,10 @@
       <c r="A15" s="6" t="s">
         <v>979</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="11" t="s">
         <v>1090</v>
       </c>
-      <c r="C15" s="7" t="str">
+      <c r="C15" s="13" t="str">
         <f t="shared" si="0"/>
         <v>sadistic reunion</v>
       </c>
@@ -15474,10 +17033,10 @@
       <c r="A16" s="6" t="s">
         <v>980</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="11" t="s">
         <v>1091</v>
       </c>
-      <c r="C16" s="7" t="str">
+      <c r="C16" s="13" t="str">
         <f t="shared" si="0"/>
         <v>suffering the consequences</v>
       </c>
@@ -15486,10 +17045,10 @@
       <c r="A17" s="6" t="s">
         <v>981</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="11" t="s">
         <v>1092</v>
       </c>
-      <c r="C17" s="7" t="str">
+      <c r="C17" s="13" t="str">
         <f t="shared" si="0"/>
         <v>everything hurts</v>
       </c>
@@ -15498,10 +17057,10 @@
       <c r="A18" s="6" t="s">
         <v>982</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="11" t="s">
         <v>1093</v>
       </c>
-      <c r="C18" s="7" t="str">
+      <c r="C18" s="13" t="str">
         <f t="shared" si="0"/>
         <v>fists of fury</v>
       </c>
@@ -15510,10 +17069,10 @@
       <c r="A19" s="6" t="s">
         <v>983</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="11" t="s">
         <v>1094</v>
       </c>
-      <c r="C19" s="7" t="str">
+      <c r="C19" s="13" t="str">
         <f t="shared" si="0"/>
         <v>bendy newcomer taken to the edge</v>
       </c>
@@ -15522,10 +17081,10 @@
       <c r="A20" s="6" t="s">
         <v>984</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="11" t="s">
         <v>1095</v>
       </c>
-      <c r="C20" s="7" t="str">
+      <c r="C20" s="13" t="str">
         <f t="shared" si="0"/>
         <v>blair bitch project</v>
       </c>
@@ -15534,10 +17093,10 @@
       <c r="A21" s="6" t="s">
         <v>985</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="11" t="s">
         <v>1096</v>
       </c>
-      <c r="C21" s="7" t="str">
+      <c r="C21" s="13" t="str">
         <f t="shared" si="0"/>
         <v>elise graves - destroyed!!!!!!!</v>
       </c>
@@ -15546,10 +17105,10 @@
       <c r="A22" s="6" t="s">
         <v>986</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="11" t="s">
         <v>1097</v>
       </c>
-      <c r="C22" s="7" t="str">
+      <c r="C22" s="13" t="str">
         <f t="shared" si="0"/>
         <v>pixie of pain</v>
       </c>
@@ -15558,10 +17117,10 @@
       <c r="A23" s="6" t="s">
         <v>987</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="11" t="s">
         <v>1098</v>
       </c>
-      <c r="C23" s="7" t="str">
+      <c r="C23" s="13" t="str">
         <f t="shared" si="0"/>
         <v>how far will she go?</v>
       </c>
@@ -15570,10 +17129,10 @@
       <c r="A24" s="6" t="s">
         <v>988</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="11" t="s">
         <v>1099</v>
       </c>
-      <c r="C24" s="7" t="str">
+      <c r="C24" s="13" t="str">
         <f t="shared" si="0"/>
         <v>destroying a bondage legend</v>
       </c>
@@ -15582,10 +17141,10 @@
       <c r="A25" s="6" t="s">
         <v>989</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="11" t="s">
         <v>1100</v>
       </c>
-      <c r="C25" s="7" t="str">
+      <c r="C25" s="13" t="str">
         <f t="shared" si="0"/>
         <v>brutality overload</v>
       </c>
@@ -15594,10 +17153,10 @@
       <c r="A26" s="6" t="s">
         <v>990</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="11" t="s">
         <v>1101</v>
       </c>
-      <c r="C26" s="7" t="str">
+      <c r="C26" s="13" t="str">
         <f t="shared" si="0"/>
         <v>role reversal</v>
       </c>
@@ -15606,10 +17165,10 @@
       <c r="A27" s="6" t="s">
         <v>991</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="11" t="s">
         <v>1102</v>
       </c>
-      <c r="C27" s="7" t="str">
+      <c r="C27" s="13" t="str">
         <f t="shared" si="0"/>
         <v>brutal bondage, total domination, and screaming orgasms.</v>
       </c>
@@ -15618,10 +17177,10 @@
       <c r="A28" s="6" t="s">
         <v>992</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="11" t="s">
         <v>1103</v>
       </c>
-      <c r="C28" s="7" t="str">
+      <c r="C28" s="13" t="str">
         <f t="shared" si="0"/>
         <v>newbie loses her mind as multiple orgasms are ripped from her body while tied and suffering.</v>
       </c>
@@ -15630,10 +17189,10 @@
       <c r="A29" s="6" t="s">
         <v>993</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="11" t="s">
         <v>1104</v>
       </c>
-      <c r="C29" s="7" t="str">
+      <c r="C29" s="13" t="str">
         <f t="shared" si="0"/>
         <v>tough slut suffers from extreme torment</v>
       </c>
@@ -15642,10 +17201,10 @@
       <c r="A30" s="6" t="s">
         <v>994</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="11" t="s">
         <v>1105</v>
       </c>
-      <c r="C30" s="7" t="str">
+      <c r="C30" s="13" t="str">
         <f t="shared" si="0"/>
         <v>ashley fires submits to the pope</v>
       </c>
@@ -15654,10 +17213,10 @@
       <c r="A31" s="6" t="s">
         <v>995</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="11" t="s">
         <v>1121</v>
       </c>
-      <c r="C31" s="7" t="str">
+      <c r="C31" s="13" t="str">
         <f t="shared" si="0"/>
         <v>minutes of suffering</v>
       </c>
@@ -15666,10 +17225,10 @@
       <c r="A32" s="6" t="s">
         <v>996</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="11" t="s">
         <v>1106</v>
       </c>
-      <c r="C32" s="7" t="str">
+      <c r="C32" s="13" t="str">
         <f t="shared" si="0"/>
         <v>beretta james has her cunt abused and over run with orgasms all day.</v>
       </c>
@@ -15678,10 +17237,10 @@
       <c r="A33" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="11" t="s">
         <v>1120</v>
       </c>
-      <c r="C33" s="7" t="str">
+      <c r="C33" s="13" t="str">
         <f t="shared" si="0"/>
         <v>sluts suffer and have uncontrollable orgasms</v>
       </c>
@@ -15690,10 +17249,10 @@
       <c r="A34" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="11" t="s">
         <v>1107</v>
       </c>
-      <c r="C34" s="7" t="str">
+      <c r="C34" s="13" t="str">
         <f t="shared" si="0"/>
         <v>keep screaming</v>
       </c>
@@ -15702,10 +17261,10 @@
       <c r="A35" s="6" t="s">
         <v>999</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="11" t="s">
         <v>1108</v>
       </c>
-      <c r="C35" s="7" t="str">
+      <c r="C35" s="13" t="str">
         <f t="shared" si="0"/>
         <v>closest to the edge</v>
       </c>
@@ -15714,10 +17273,10 @@
       <c r="A36" s="6" t="s">
         <v>1000</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="11" t="s">
         <v>1109</v>
       </c>
-      <c r="C36" s="7" t="str">
+      <c r="C36" s="13" t="str">
         <f t="shared" si="0"/>
         <v>elizabeth thorn - edited live show</v>
       </c>
@@ -15726,10 +17285,10 @@
       <c r="A37" s="6" t="s">
         <v>1001</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="11" t="s">
         <v>1110</v>
       </c>
-      <c r="C37" s="7" t="str">
+      <c r="C37" s="13" t="str">
         <f t="shared" si="0"/>
         <v>penny is tormented in tight bondage!</v>
       </c>
@@ -15738,10 +17297,10 @@
       <c r="A38" s="6" t="s">
         <v>1002</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="11" t="s">
         <v>1111</v>
       </c>
-      <c r="C38" s="7" t="str">
+      <c r="C38" s="13" t="str">
         <f t="shared" si="0"/>
         <v>hard bodied slut gets debased</v>
       </c>
@@ -15750,10 +17309,10 @@
       <c r="A39" s="6" t="s">
         <v>1003</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="11" t="s">
         <v>1112</v>
       </c>
-      <c r="C39" s="7" t="str">
+      <c r="C39" s="13" t="str">
         <f t="shared" si="0"/>
         <v>tight rope bondage, brutal torment, and extreme orgasms</v>
       </c>
@@ -15762,10 +17321,10 @@
       <c r="A40" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="11" t="s">
         <v>1113</v>
       </c>
-      <c r="C40" s="7" t="str">
+      <c r="C40" s="13" t="str">
         <f t="shared" si="0"/>
         <v>brutal torment of one whore by two sick fucks!-live show edited</v>
       </c>
@@ -15774,10 +17333,10 @@
       <c r="A41" s="6" t="s">
         <v>1005</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="11" t="s">
         <v>1114</v>
       </c>
-      <c r="C41" s="7" t="str">
+      <c r="C41" s="13" t="str">
         <f t="shared" si="0"/>
         <v>young, helpless slut suffers through brutal bondage</v>
       </c>
@@ -15786,10 +17345,10 @@
       <c r="A42" s="6" t="s">
         <v>1006</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="11" t="s">
         <v>1115</v>
       </c>
-      <c r="C42" s="7" t="str">
+      <c r="C42" s="13" t="str">
         <f t="shared" si="0"/>
         <v>skin diamond-brutal bondage, extreme suffering, and screaming orgasms!</v>
       </c>
@@ -15798,10 +17357,10 @@
       <c r="A43" s="6" t="s">
         <v>1007</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="11" t="s">
         <v>1116</v>
       </c>
-      <c r="C43" s="7" t="str">
+      <c r="C43" s="13" t="str">
         <f t="shared" si="0"/>
         <v>elise graves gets destroyed by brutal bondage!!!</v>
       </c>
@@ -15810,10 +17369,10 @@
       <c r="A44" s="6" t="s">
         <v>1008</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="11" t="s">
         <v>1117</v>
       </c>
-      <c r="C44" s="7" t="str">
+      <c r="C44" s="13" t="str">
         <f t="shared" si="0"/>
         <v>rope slut endures extreme torment!!!!</v>
       </c>
@@ -15822,10 +17381,10 @@
       <c r="A45" s="6" t="s">
         <v>1009</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="11" t="s">
         <v>1118</v>
       </c>
-      <c r="C45" s="7" t="str">
+      <c r="C45" s="13" t="str">
         <f t="shared" si="0"/>
         <v>the pope destroys lorelei lee!!!</v>
       </c>
@@ -15834,10 +17393,10 @@
       <c r="A46" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="11" t="s">
         <v>1010</v>
       </c>
-      <c r="C46" s="7" t="str">
+      <c r="C46" s="13" t="str">
         <f t="shared" si="0"/>
         <v>submissive slut in devastating bondage!!</v>
       </c>
@@ -15846,10 +17405,10 @@
       <c r="A47" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="11" t="s">
         <v>1011</v>
       </c>
-      <c r="C47" s="7" t="str">
+      <c r="C47" s="13" t="str">
         <f t="shared" si="0"/>
         <v>warning!! extreme torment, bondage, and water boarding</v>
       </c>
@@ -15858,10 +17417,10 @@
       <c r="A48" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="11" t="s">
         <v>1012</v>
       </c>
-      <c r="C48" s="7" t="str">
+      <c r="C48" s="13" t="str">
         <f t="shared" si="0"/>
         <v>samoan slut with natural big tits is punished!</v>
       </c>
@@ -15870,10 +17429,10 @@
       <c r="A49" s="6" t="s">
         <v>1013</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="11" t="s">
         <v>1013</v>
       </c>
-      <c r="C49" s="7" t="str">
+      <c r="C49" s="13" t="str">
         <f t="shared" si="0"/>
         <v>hot young blonde suffers from brutal torment in tight bondage</v>
       </c>
@@ -15882,10 +17441,10 @@
       <c r="A50" s="6" t="s">
         <v>1014</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="11" t="s">
         <v>1014</v>
       </c>
-      <c r="C50" s="7" t="str">
+      <c r="C50" s="13" t="str">
         <f t="shared" si="0"/>
         <v>dahlia sky gets destroyed with brutal bondage and extreme torture</v>
       </c>
@@ -15894,10 +17453,10 @@
       <c r="A51" s="6" t="s">
         <v>1015</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="11" t="s">
         <v>1015</v>
       </c>
-      <c r="C51" s="7" t="str">
+      <c r="C51" s="13" t="str">
         <f t="shared" si="0"/>
         <v>brand new pain slut does her first shoot ever!!!</v>
       </c>
@@ -15906,10 +17465,10 @@
       <c r="A52" s="6" t="s">
         <v>1016</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="11" t="s">
         <v>1016</v>
       </c>
-      <c r="C52" s="7" t="str">
+      <c r="C52" s="13" t="str">
         <f t="shared" si="0"/>
         <v>more than she bargained for!</v>
       </c>
@@ -15918,10 +17477,10 @@
       <c r="A53" s="6" t="s">
         <v>1017</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="11" t="s">
         <v>1017</v>
       </c>
-      <c r="C53" s="7" t="str">
+      <c r="C53" s="13" t="str">
         <f t="shared" si="0"/>
         <v>andre suffers in extreme bondage and brutal torment</v>
       </c>
@@ -15930,10 +17489,10 @@
       <c r="A54" s="6" t="s">
         <v>1018</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="11" t="s">
         <v>1018</v>
       </c>
-      <c r="C54" s="7" t="str">
+      <c r="C54" s="13" t="str">
         <f t="shared" si="0"/>
         <v>small asian takes massive fist while bound</v>
       </c>
@@ -15942,10 +17501,10 @@
       <c r="A55" s="6" t="s">
         <v>1019</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="11" t="s">
         <v>1019</v>
       </c>
-      <c r="C55" s="7" t="str">
+      <c r="C55" s="13" t="str">
         <f t="shared" si="0"/>
         <v>ebony slut is tied and tormented</v>
       </c>
@@ -15954,10 +17513,10 @@
       <c r="A56" s="6" t="s">
         <v>1020</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="11" t="s">
         <v>1020</v>
       </c>
-      <c r="C56" s="7" t="str">
+      <c r="C56" s="13" t="str">
         <f t="shared" si="0"/>
         <v>newbie gets a lesson in suffering at the hands of the meanest man in the industry</v>
       </c>
@@ -15966,10 +17525,10 @@
       <c r="A57" s="6" t="s">
         <v>1021</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="11" t="s">
         <v>1021</v>
       </c>
-      <c r="C57" s="7" t="str">
+      <c r="C57" s="13" t="str">
         <f t="shared" si="0"/>
         <v>fisting, water boarding, extreme torment, and brutal bondage!!!</v>
       </c>
@@ -15978,10 +17537,10 @@
       <c r="A58" s="6" t="s">
         <v>1022</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="11" t="s">
         <v>1022</v>
       </c>
-      <c r="C58" s="7" t="str">
+      <c r="C58" s="13" t="str">
         <f t="shared" si="0"/>
         <v>hot blonde suffers through an extreme beating while in tight bondage</v>
       </c>
@@ -15990,10 +17549,10 @@
       <c r="A59" s="6" t="s">
         <v>1023</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="11" t="s">
         <v>1023</v>
       </c>
-      <c r="C59" s="7" t="str">
+      <c r="C59" s="13" t="str">
         <f t="shared" si="0"/>
         <v>blonde big tit milf gets punished</v>
       </c>
@@ -16002,10 +17561,10 @@
       <c r="A60" s="6" t="s">
         <v>1024</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="11" t="s">
         <v>1024</v>
       </c>
-      <c r="C60" s="7" t="str">
+      <c r="C60" s="13" t="str">
         <f t="shared" si="0"/>
         <v>the pope vs darling</v>
       </c>
@@ -16014,10 +17573,10 @@
       <c r="A61" s="6" t="s">
         <v>1025</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="11" t="s">
         <v>1025</v>
       </c>
-      <c r="C61" s="7" t="str">
+      <c r="C61" s="13" t="str">
         <f t="shared" si="0"/>
         <v>2 whores = twice the suffering</v>
       </c>
@@ -16026,10 +17585,10 @@
       <c r="A62" s="6" t="s">
         <v>1026</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="11" t="s">
         <v>1026</v>
       </c>
-      <c r="C62" s="7" t="str">
+      <c r="C62" s="13" t="str">
         <f t="shared" si="0"/>
         <v>all natural, girl next door suffering!!!</v>
       </c>
@@ -16038,10 +17597,10 @@
       <c r="A63" s="6" t="s">
         <v>1027</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="11" t="s">
         <v>1027</v>
       </c>
-      <c r="C63" s="7" t="str">
+      <c r="C63" s="13" t="str">
         <f t="shared" si="0"/>
         <v>the pope brutally tortures newcomer, sophia locke</v>
       </c>
@@ -16050,10 +17609,10 @@
       <c r="A64" s="6" t="s">
         <v>1028</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="11" t="s">
         <v>1028</v>
       </c>
-      <c r="C64" s="7" t="str">
+      <c r="C64" s="13" t="str">
         <f t="shared" si="0"/>
         <v>the pope abuses casey calvert in her toughest shoot to date!!!</v>
       </c>
@@ -16062,10 +17621,10 @@
       <c r="A65" s="6" t="s">
         <v>1029</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="11" t="s">
         <v>1029</v>
       </c>
-      <c r="C65" s="7" t="str">
+      <c r="C65" s="13" t="str">
         <f t="shared" si="0"/>
         <v>california girl gets destroyed by intense bondage and brutal torture</v>
       </c>
@@ -16074,10 +17633,10 @@
       <c r="A66" s="6" t="s">
         <v>1030</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="11" t="s">
         <v>1030</v>
       </c>
-      <c r="C66" s="7" t="str">
+      <c r="C66" s="13" t="str">
         <f t="shared" si="0"/>
         <v>hot slut is fisted by the pope's massive fist!!!</v>
       </c>
@@ -16086,10 +17645,10 @@
       <c r="A67" s="6" t="s">
         <v>1031</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="11" t="s">
         <v>1031</v>
       </c>
-      <c r="C67" s="7" t="str">
+      <c r="C67" s="13" t="str">
         <f t="shared" ref="C67:C112" si="1">LOWER(B67)</f>
         <v>extreme bondage, orgasm overload, brutal torture, hair suspension!</v>
       </c>
@@ -16098,10 +17657,10 @@
       <c r="A68" s="6" t="s">
         <v>1032</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="11" t="s">
         <v>1032</v>
       </c>
-      <c r="C68" s="7" t="str">
+      <c r="C68" s="13" t="str">
         <f t="shared" si="1"/>
         <v>young slut with huge natural tits gets destroyed by grueling bondage</v>
       </c>
@@ -16110,10 +17669,10 @@
       <c r="A69" s="6" t="s">
         <v>1033</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="11" t="s">
         <v>1033</v>
       </c>
-      <c r="C69" s="7" t="str">
+      <c r="C69" s="13" t="str">
         <f t="shared" si="1"/>
         <v>hot blonde pain slut suffers through grueling suspension bondage</v>
       </c>
@@ -16122,10 +17681,10 @@
       <c r="A70" s="6" t="s">
         <v>1034</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="11" t="s">
         <v>1034</v>
       </c>
-      <c r="C70" s="7" t="str">
+      <c r="C70" s="13" t="str">
         <f t="shared" si="1"/>
         <v>the pope teaches this newcomer what bondage is all about</v>
       </c>
@@ -16134,10 +17693,10 @@
       <c r="A71" s="6" t="s">
         <v>1035</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="11" t="s">
         <v>1035</v>
       </c>
-      <c r="C71" s="7" t="str">
+      <c r="C71" s="13" t="str">
         <f t="shared" si="1"/>
         <v>hot blonde suffers for 2 hours without any breaks</v>
       </c>
@@ -16146,10 +17705,10 @@
       <c r="A72" s="6" t="s">
         <v>1036</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="11" t="s">
         <v>1036</v>
       </c>
-      <c r="C72" s="7" t="str">
+      <c r="C72" s="13" t="str">
         <f t="shared" si="1"/>
         <v>new girl suffers through extreme torment</v>
       </c>
@@ -16158,10 +17717,10 @@
       <c r="A73" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="11" t="s">
         <v>1037</v>
       </c>
-      <c r="C73" s="7" t="str">
+      <c r="C73" s="13" t="str">
         <f t="shared" si="1"/>
         <v>squirting from pain</v>
       </c>
@@ -16170,10 +17729,10 @@
       <c r="A74" s="6" t="s">
         <v>1038</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="11" t="s">
         <v>1038</v>
       </c>
-      <c r="C74" s="7" t="str">
+      <c r="C74" s="13" t="str">
         <f t="shared" si="1"/>
         <v>asian bondage slut gets destroyed!</v>
       </c>
@@ -16182,10 +17741,10 @@
       <c r="A75" s="6" t="s">
         <v>1039</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="11" t="s">
         <v>1039</v>
       </c>
-      <c r="C75" s="7" t="str">
+      <c r="C75" s="13" t="str">
         <f t="shared" si="1"/>
         <v>hot japanese bondage slut suffers in grueling bondage</v>
       </c>
@@ -16194,10 +17753,10 @@
       <c r="A76" s="6" t="s">
         <v>1040</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="11" t="s">
         <v>1040</v>
       </c>
-      <c r="C76" s="7" t="str">
+      <c r="C76" s="13" t="str">
         <f t="shared" si="1"/>
         <v>hot milf, simone sonay, suffers in brutal bondage</v>
       </c>
@@ -16206,10 +17765,10 @@
       <c r="A77" s="6" t="s">
         <v>1041</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="11" t="s">
         <v>1041</v>
       </c>
-      <c r="C77" s="7" t="str">
+      <c r="C77" s="13" t="str">
         <f t="shared" si="1"/>
         <v>bratty slut submits, but not without a fight!</v>
       </c>
@@ -16218,10 +17777,10 @@
       <c r="A78" s="6" t="s">
         <v>1042</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="11" t="s">
         <v>1042</v>
       </c>
-      <c r="C78" s="7" t="str">
+      <c r="C78" s="13" t="str">
         <f t="shared" si="1"/>
         <v>skin diamond-tight bondage, insane torment, extreme orgasms!!</v>
       </c>
@@ -16230,10 +17789,10 @@
       <c r="A79" s="6" t="s">
         <v>1043</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="B79" s="11" t="s">
         <v>1043</v>
       </c>
-      <c r="C79" s="7" t="str">
+      <c r="C79" s="13" t="str">
         <f t="shared" si="1"/>
         <v>the pope destroys a newcomer</v>
       </c>
@@ -16242,10 +17801,10 @@
       <c r="A80" s="6" t="s">
         <v>1044</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="B80" s="11" t="s">
         <v>1044</v>
       </c>
-      <c r="C80" s="7" t="str">
+      <c r="C80" s="13" t="str">
         <f t="shared" si="1"/>
         <v>lyla storm's most hardcore shoot ever!!!</v>
       </c>
@@ -16254,10 +17813,10 @@
       <c r="A81" s="6" t="s">
         <v>1045</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="B81" s="11" t="s">
         <v>1045</v>
       </c>
-      <c r="C81" s="7" t="str">
+      <c r="C81" s="13" t="str">
         <f t="shared" si="1"/>
         <v>warning: devastating brutality and torment!</v>
       </c>
@@ -16266,10 +17825,10 @@
       <c r="A82" s="6" t="s">
         <v>1046</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="B82" s="11" t="s">
         <v>1046</v>
       </c>
-      <c r="C82" s="7" t="str">
+      <c r="C82" s="13" t="str">
         <f t="shared" si="1"/>
         <v>the pope torments dahlia sky for 2 hours with non-stop brutality!</v>
       </c>
@@ -16278,10 +17837,10 @@
       <c r="A83" s="6" t="s">
         <v>1047</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="B83" s="11" t="s">
         <v>1047</v>
       </c>
-      <c r="C83" s="7" t="str">
+      <c r="C83" s="13" t="str">
         <f t="shared" si="1"/>
         <v>hot young slut in brutal bondage suffering</v>
       </c>
@@ -16290,10 +17849,10 @@
       <c r="A84" s="6" t="s">
         <v>1048</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B84" s="11" t="s">
         <v>1048</v>
       </c>
-      <c r="C84" s="7" t="str">
+      <c r="C84" s="13" t="str">
         <f t="shared" si="1"/>
         <v>slut spanked into submission</v>
       </c>
@@ -16302,10 +17861,10 @@
       <c r="A85" s="6" t="s">
         <v>1049</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="B85" s="11" t="s">
         <v>1049</v>
       </c>
-      <c r="C85" s="7" t="str">
+      <c r="C85" s="13" t="str">
         <f t="shared" si="1"/>
         <v>super hot slut gets her first taste of bondage</v>
       </c>
@@ -16314,10 +17873,10 @@
       <c r="A86" s="6" t="s">
         <v>1050</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="B86" s="11" t="s">
         <v>1050</v>
       </c>
-      <c r="C86" s="7" t="str">
+      <c r="C86" s="13" t="str">
         <f t="shared" si="1"/>
         <v>hot young latin whore suffering</v>
       </c>
@@ -16326,10 +17885,10 @@
       <c r="A87" s="6" t="s">
         <v>1051</v>
       </c>
-      <c r="B87" s="6" t="s">
+      <c r="B87" s="11" t="s">
         <v>1051</v>
       </c>
-      <c r="C87" s="7" t="str">
+      <c r="C87" s="13" t="str">
         <f t="shared" si="1"/>
         <v>sexy ebony slut begs to be taken to the edge</v>
       </c>
@@ -16338,10 +17897,10 @@
       <c r="A88" s="6" t="s">
         <v>1052</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="B88" s="11" t="s">
         <v>1052</v>
       </c>
-      <c r="C88" s="7" t="str">
+      <c r="C88" s="13" t="str">
         <f t="shared" si="1"/>
         <v>ella nova is tormented in extreme bondage</v>
       </c>
@@ -16350,10 +17909,10 @@
       <c r="A89" s="6" t="s">
         <v>1053</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="B89" s="11" t="s">
         <v>1053</v>
       </c>
-      <c r="C89" s="7" t="str">
+      <c r="C89" s="13" t="str">
         <f t="shared" si="1"/>
         <v>hot wrestler gets her ass handed to her by the pope</v>
       </c>
@@ -16362,10 +17921,10 @@
       <c r="A90" s="6" t="s">
         <v>1054</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="B90" s="11" t="s">
         <v>1054</v>
       </c>
-      <c r="C90" s="7" t="str">
+      <c r="C90" s="13" t="str">
         <f t="shared" si="1"/>
         <v>un-cut, nonstop action with brutal bondage and squirting orgasms</v>
       </c>
@@ -16374,10 +17933,10 @@
       <c r="A91" s="6" t="s">
         <v>1055</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="B91" s="11" t="s">
         <v>1055</v>
       </c>
-      <c r="C91" s="7" t="str">
+      <c r="C91" s="13" t="str">
         <f t="shared" si="1"/>
         <v>new comer gets her first taste of extreme bondage</v>
       </c>
@@ -16386,10 +17945,10 @@
       <c r="A92" s="6" t="s">
         <v>1056</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="B92" s="11" t="s">
         <v>1056</v>
       </c>
-      <c r="C92" s="7" t="str">
+      <c r="C92" s="13" t="str">
         <f t="shared" si="1"/>
         <v>katt anomia wants the full treatment!!!</v>
       </c>
@@ -16398,10 +17957,10 @@
       <c r="A93" s="6" t="s">
         <v>1057</v>
       </c>
-      <c r="B93" s="6" t="s">
+      <c r="B93" s="11" t="s">
         <v>1057</v>
       </c>
-      <c r="C93" s="7" t="str">
+      <c r="C93" s="13" t="str">
         <f t="shared" si="1"/>
         <v>ariel x - bound and squirting</v>
       </c>
@@ -16410,10 +17969,10 @@
       <c r="A94" s="6" t="s">
         <v>1058</v>
       </c>
-      <c r="B94" s="6" t="s">
+      <c r="B94" s="11" t="s">
         <v>1058</v>
       </c>
-      <c r="C94" s="7" t="str">
+      <c r="C94" s="13" t="str">
         <f t="shared" si="1"/>
         <v>carmen caliente in tight bondage and screaming</v>
       </c>
@@ -16422,10 +17981,10 @@
       <c r="A95" s="6" t="s">
         <v>1059</v>
       </c>
-      <c r="B95" s="6" t="s">
+      <c r="B95" s="11" t="s">
         <v>1059</v>
       </c>
-      <c r="C95" s="7" t="str">
+      <c r="C95" s="13" t="str">
         <f t="shared" si="1"/>
         <v>veruca james in intense predicament bondage</v>
       </c>
@@ -16434,10 +17993,10 @@
       <c r="A96" s="6" t="s">
         <v>1060</v>
       </c>
-      <c r="B96" s="6" t="s">
+      <c r="B96" s="11" t="s">
         <v>1060</v>
       </c>
-      <c r="C96" s="7" t="str">
+      <c r="C96" s="13" t="str">
         <f t="shared" si="1"/>
         <v>hot latina, kristina rose in tight bondage and suffering</v>
       </c>
@@ -16446,10 +18005,10 @@
       <c r="A97" s="6" t="s">
         <v>1061</v>
       </c>
-      <c r="B97" s="6" t="s">
+      <c r="B97" s="11" t="s">
         <v>1061</v>
       </c>
-      <c r="C97" s="7" t="str">
+      <c r="C97" s="13" t="str">
         <f t="shared" si="1"/>
         <v>ariel x submits!!</v>
       </c>
@@ -16458,10 +18017,10 @@
       <c r="A98" s="6" t="s">
         <v>1062</v>
       </c>
-      <c r="B98" s="6" t="s">
+      <c r="B98" s="11" t="s">
         <v>1062</v>
       </c>
-      <c r="C98" s="7" t="str">
+      <c r="C98" s="13" t="str">
         <f t="shared" si="1"/>
         <v>hot latina is helpless in agonizing bondage</v>
       </c>
@@ -16470,10 +18029,10 @@
       <c r="A99" s="6" t="s">
         <v>1063</v>
       </c>
-      <c r="B99" s="6" t="s">
+      <c r="B99" s="11" t="s">
         <v>1063</v>
       </c>
-      <c r="C99" s="7" t="str">
+      <c r="C99" s="13" t="str">
         <f t="shared" si="1"/>
         <v>casey calvert suffers in grueling bondage!!</v>
       </c>
@@ -16482,10 +18041,10 @@
       <c r="A100" s="6" t="s">
         <v>1064</v>
       </c>
-      <c r="B100" s="6" t="s">
+      <c r="B100" s="11" t="s">
         <v>1064</v>
       </c>
-      <c r="C100" s="7" t="str">
+      <c r="C100" s="13" t="str">
         <f t="shared" si="1"/>
         <v>mona wales tied up and tormented</v>
       </c>
@@ -16494,10 +18053,10 @@
       <c r="A101" s="6" t="s">
         <v>1065</v>
       </c>
-      <c r="B101" s="6" t="s">
+      <c r="B101" s="11" t="s">
         <v>1065</v>
       </c>
-      <c r="C101" s="7" t="str">
+      <c r="C101" s="13" t="str">
         <f t="shared" si="1"/>
         <v>water torment in strict bondage with squirting orgasms</v>
       </c>
@@ -16506,10 +18065,10 @@
       <c r="A102" s="6" t="s">
         <v>1066</v>
       </c>
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="11" t="s">
         <v>1066</v>
       </c>
-      <c r="C102" s="7" t="str">
+      <c r="C102" s="13" t="str">
         <f t="shared" si="1"/>
         <v>the pope destroys dani daniels!!!!</v>
       </c>
@@ -16518,10 +18077,10 @@
       <c r="A103" s="6" t="s">
         <v>1067</v>
       </c>
-      <c r="B103" s="6" t="s">
+      <c r="B103" s="11" t="s">
         <v>1067</v>
       </c>
-      <c r="C103" s="7" t="str">
+      <c r="C103" s="13" t="str">
         <f t="shared" si="1"/>
         <v>brunette hottie in extreme bondage!</v>
       </c>
@@ -16530,10 +18089,10 @@
       <c r="A104" s="6" t="s">
         <v>1068</v>
       </c>
-      <c r="B104" s="6" t="s">
+      <c r="B104" s="11" t="s">
         <v>1068</v>
       </c>
-      <c r="C104" s="7" t="str">
+      <c r="C104" s="13" t="str">
         <f t="shared" si="1"/>
         <v>hot petite slut in brutal bondage with devastating torment</v>
       </c>
@@ -16542,10 +18101,10 @@
       <c r="A105" s="6" t="s">
         <v>1069</v>
       </c>
-      <c r="B105" s="6" t="s">
+      <c r="B105" s="11" t="s">
         <v>1069</v>
       </c>
-      <c r="C105" s="7" t="str">
+      <c r="C105" s="13" t="str">
         <f t="shared" si="1"/>
         <v>brand new girl in brutal bondage with extreme torment!!</v>
       </c>
@@ -16554,10 +18113,10 @@
       <c r="A106" s="6" t="s">
         <v>1070</v>
       </c>
-      <c r="B106" s="6" t="s">
+      <c r="B106" s="11" t="s">
         <v>1070</v>
       </c>
-      <c r="C106" s="7" t="str">
+      <c r="C106" s="13" t="str">
         <f t="shared" si="1"/>
         <v>inspired suffering</v>
       </c>
@@ -16566,10 +18125,10 @@
       <c r="A107" s="6" t="s">
         <v>1071</v>
       </c>
-      <c r="B107" s="6" t="s">
+      <c r="B107" s="11" t="s">
         <v>1071</v>
       </c>
-      <c r="C107" s="7" t="str">
+      <c r="C107" s="13" t="str">
         <f t="shared" si="1"/>
         <v>the destruction of sophia locke</v>
       </c>
@@ -16578,10 +18137,10 @@
       <c r="A108" s="6" t="s">
         <v>1072</v>
       </c>
-      <c r="B108" s="6" t="s">
+      <c r="B108" s="11" t="s">
         <v>1072</v>
       </c>
-      <c r="C108" s="7" t="str">
+      <c r="C108" s="13" t="str">
         <f t="shared" si="1"/>
         <v>bit tits, brutal bondage, severe beatings and breath play</v>
       </c>
@@ -16590,10 +18149,10 @@
       <c r="A109" s="6" t="s">
         <v>1073</v>
       </c>
-      <c r="B109" s="6" t="s">
+      <c r="B109" s="11" t="s">
         <v>1073</v>
       </c>
-      <c r="C109" s="7" t="str">
+      <c r="C109" s="13" t="str">
         <f t="shared" si="1"/>
         <v>casey calvert exposed!!</v>
       </c>
@@ -16602,10 +18161,10 @@
       <c r="A110" s="6" t="s">
         <v>1074</v>
       </c>
-      <c r="B110" s="6" t="s">
+      <c r="B110" s="11" t="s">
         <v>1074</v>
       </c>
-      <c r="C110" s="7" t="str">
+      <c r="C110" s="13" t="str">
         <f t="shared" si="1"/>
         <v>pain slut in extreme bondage with brutal pain domination!!!</v>
       </c>
@@ -16614,10 +18173,10 @@
       <c r="A111" s="6" t="s">
         <v>1075</v>
       </c>
-      <c r="B111" s="6" t="s">
+      <c r="B111" s="11" t="s">
         <v>1075</v>
       </c>
-      <c r="C111" s="7" t="str">
+      <c r="C111" s="13" t="str">
         <f t="shared" si="1"/>
         <v>phoenix marie and delirious hunter suffer for the pope</v>
       </c>
@@ -16626,1371 +18185,1376 @@
       <c r="A112" s="6" t="s">
         <v>1076</v>
       </c>
-      <c r="B112" s="6" t="s">
+      <c r="B112" s="11" t="s">
         <v>1076</v>
       </c>
-      <c r="C112" s="7" t="str">
+      <c r="C112" s="13" t="str">
         <f t="shared" si="1"/>
         <v>the pope destroys abella danger!!</v>
       </c>
     </row>
+    <row r="113" spans="3:3" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="C113" s="14" t="s">
+        <v>1332</v>
+      </c>
+    </row>
     <row r="114" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C114" s="8" t="s">
+      <c r="C114" s="6" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="115" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C115" s="8" t="s">
+      <c r="C115" s="6" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="116" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C116" s="8" t="s">
+      <c r="C116" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="117" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C117" s="8" t="s">
+      <c r="C117" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="118" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C118" s="8" t="s">
+      <c r="C118" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="119" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C119" s="8" t="s">
+      <c r="C119" s="6" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="120" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C120" s="8" t="s">
+      <c r="C120" s="6" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="121" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C121" s="8" t="s">
+      <c r="C121" s="6" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="122" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C122" s="8" t="s">
+      <c r="C122" s="6" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="123" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C123" s="8" t="s">
+      <c r="C123" s="6" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="124" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C124" s="8" t="s">
+      <c r="C124" s="6" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="125" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="6" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="126" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C126" s="8" t="s">
+      <c r="C126" s="6" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="127" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="128" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C128" s="8" t="s">
+      <c r="C128" s="6" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="129" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C129" s="8" t="s">
+      <c r="C129" s="6" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="130" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C130" s="8" t="s">
+      <c r="C130" s="6" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="131" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="6" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="132" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C132" s="8" t="s">
+      <c r="C132" s="6" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="133" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C133" s="8" t="s">
+      <c r="C133" s="6" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="134" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C134" s="8" t="s">
+      <c r="C134" s="6" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="135" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C135" s="8" t="s">
+      <c r="C135" s="6" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="136" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C136" s="8" t="s">
+      <c r="C136" s="6" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="137" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C137" s="8" t="s">
+      <c r="C137" s="6" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="138" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C138" s="8" t="s">
+      <c r="C138" s="6" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="139" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C139" s="8" t="s">
+      <c r="C139" s="6" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="140" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C140" s="8" t="s">
+      <c r="C140" s="6" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="141" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C141" s="8" t="s">
+      <c r="C141" s="6" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="142" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C142" s="8" t="s">
+      <c r="C142" s="6" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="143" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C143" s="8" t="s">
+      <c r="C143" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="144" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C144" s="8" t="s">
+      <c r="C144" s="6" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="145" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C145" s="8" t="s">
+      <c r="C145" s="6" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="146" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C146" s="8" t="s">
+      <c r="C146" s="6" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="147" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C147" s="8" t="s">
+      <c r="C147" s="6" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="148" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C148" s="8" t="s">
+      <c r="C148" s="6" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="149" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C149" s="8" t="s">
+      <c r="C149" s="6" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="150" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C150" s="8" t="s">
+      <c r="C150" s="6" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="151" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C151" s="8" t="s">
+      <c r="C151" s="6" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="152" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C152" s="8" t="s">
+      <c r="C152" s="6" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="153" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C153" s="8" t="s">
+      <c r="C153" s="6" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="154" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C154" s="8" t="s">
+      <c r="C154" s="6" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="155" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C155" s="8" t="s">
+      <c r="C155" s="6" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="156" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C156" s="8" t="s">
+      <c r="C156" s="6" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="157" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C157" s="8" t="s">
+      <c r="C157" s="6" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="158" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C158" s="8" t="s">
+      <c r="C158" s="6" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="159" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C159" s="8" t="s">
+      <c r="C159" s="6" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="160" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C160" s="8" t="s">
+      <c r="C160" s="6" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="161" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C161" s="8" t="s">
+      <c r="C161" s="6" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="162" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C162" s="8" t="s">
+      <c r="C162" s="6" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="163" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C163" s="8" t="s">
+      <c r="C163" s="6" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="164" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C164" s="8" t="s">
+      <c r="C164" s="6" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="165" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C165" s="8" t="s">
+      <c r="C165" s="6" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="166" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C166" s="8" t="s">
+      <c r="C166" s="6" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="167" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C167" s="8" t="s">
+      <c r="C167" s="6" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="168" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C168" s="8" t="s">
+      <c r="C168" s="6" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="169" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C169" s="8" t="s">
+      <c r="C169" s="6" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="170" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C170" s="8" t="s">
+      <c r="C170" s="6" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="171" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C171" s="8" t="s">
+      <c r="C171" s="6" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="172" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C172" s="8" t="s">
+      <c r="C172" s="6" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="173" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C173" s="8" t="s">
+      <c r="C173" s="6" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="174" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C174" s="8" t="s">
+      <c r="C174" s="6" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="175" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C175" s="8" t="s">
+      <c r="C175" s="6" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="176" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C176" s="8" t="s">
+      <c r="C176" s="6" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="177" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C177" s="8" t="s">
+      <c r="C177" s="6" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="178" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C178" s="8" t="s">
+      <c r="C178" s="6" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="179" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C179" s="8" t="s">
+      <c r="C179" s="6" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="180" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C180" s="8" t="s">
+      <c r="C180" s="6" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="181" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C181" s="8" t="s">
+      <c r="C181" s="6" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="182" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C182" s="8" t="s">
+      <c r="C182" s="6" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="183" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C183" s="8" t="s">
+      <c r="C183" s="6" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="184" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C184" s="8" t="s">
+      <c r="C184" s="6" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="185" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C185" s="8" t="s">
+      <c r="C185" s="6" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="186" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C186" s="8" t="s">
+      <c r="C186" s="6" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="187" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C187" s="8" t="s">
+      <c r="C187" s="6" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="188" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C188" s="8" t="s">
+      <c r="C188" s="6" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="189" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C189" s="8" t="s">
+      <c r="C189" s="6" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="190" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C190" s="8" t="s">
+      <c r="C190" s="6" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="191" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C191" s="8" t="s">
+      <c r="C191" s="6" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="192" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C192" s="8" t="s">
+      <c r="C192" s="6" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="193" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C193" s="8" t="s">
+      <c r="C193" s="6" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="194" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C194" s="8" t="s">
+      <c r="C194" s="6" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="195" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C195" s="8" t="s">
+      <c r="C195" s="6" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="196" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C196" s="8" t="s">
+      <c r="C196" s="6" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="197" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C197" s="8" t="s">
+      <c r="C197" s="6" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="198" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C198" s="8" t="s">
+      <c r="C198" s="6" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="199" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C199" s="8" t="s">
+      <c r="C199" s="6" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="200" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C200" s="8" t="s">
+      <c r="C200" s="6" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="201" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C201" s="8" t="s">
+      <c r="C201" s="6" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="202" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C202" s="8" t="s">
+      <c r="C202" s="6" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="203" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C203" s="8" t="s">
+      <c r="C203" s="6" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="204" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C204" s="8" t="s">
+      <c r="C204" s="6" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="205" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C205" s="8" t="s">
+      <c r="C205" s="6" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="206" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C206" s="8" t="s">
+      <c r="C206" s="6" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="207" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C207" s="8" t="s">
+      <c r="C207" s="6" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="208" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C208" s="8" t="s">
+      <c r="C208" s="6" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="209" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C209" s="8" t="s">
+      <c r="C209" s="6" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="210" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C210" s="8" t="s">
+      <c r="C210" s="6" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="211" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C211" s="8" t="s">
+      <c r="C211" s="6" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="212" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C212" s="8" t="s">
+      <c r="C212" s="6" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="213" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C213" s="8" t="s">
+      <c r="C213" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="214" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C214" s="8" t="s">
+      <c r="C214" s="6" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="215" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C215" s="8" t="s">
+      <c r="C215" s="6" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="216" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C216" s="8" t="s">
+      <c r="C216" s="6" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="217" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C217" s="8" t="s">
+      <c r="C217" s="6" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="218" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C218" s="8" t="s">
+      <c r="C218" s="6" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="219" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C219" s="8" t="s">
+      <c r="C219" s="6" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="220" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C220" s="8" t="s">
+      <c r="C220" s="6" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="221" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C221" s="8" t="s">
+      <c r="C221" s="6" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="222" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C222" s="8" t="s">
+      <c r="C222" s="6" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="223" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C223" s="8" t="s">
+      <c r="C223" s="6" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="224" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C224" s="8" t="s">
+      <c r="C224" s="6" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="225" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C225" s="8" t="s">
+      <c r="C225" s="6" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="226" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C226" s="8" t="s">
+      <c r="C226" s="6" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="227" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C227" s="8" t="s">
+      <c r="C227" s="6" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="228" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C228" s="8" t="s">
+      <c r="C228" s="6" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="229" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C229" s="8" t="s">
+      <c r="C229" s="6" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="230" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C230" s="8" t="s">
+      <c r="C230" s="6" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="231" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C231" s="8" t="s">
+      <c r="C231" s="6" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="232" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C232" s="8" t="s">
+      <c r="C232" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="233" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C233" s="8" t="s">
+      <c r="C233" s="6" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="234" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C234" s="8" t="s">
+      <c r="C234" s="6" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="235" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C235" s="8" t="s">
+      <c r="C235" s="6" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="236" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C236" s="8" t="s">
+      <c r="C236" s="6" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="237" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C237" s="8" t="s">
+      <c r="C237" s="6" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="238" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C238" s="8" t="s">
+      <c r="C238" s="6" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="239" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C239" s="8" t="s">
+      <c r="C239" s="6" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="240" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C240" s="8" t="s">
+      <c r="C240" s="6" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="241" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C241" s="8" t="s">
+      <c r="C241" s="6" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="242" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C242" s="8" t="s">
+      <c r="C242" s="6" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="243" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C243" s="8" t="s">
+      <c r="C243" s="6" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="244" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C244" s="8" t="s">
+      <c r="C244" s="6" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="245" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C245" s="8" t="s">
+      <c r="C245" s="6" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="246" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C246" s="8" t="s">
+      <c r="C246" s="6" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="247" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C247" s="8" t="s">
+      <c r="C247" s="6" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="248" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C248" s="8" t="s">
+      <c r="C248" s="6" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="249" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C249" s="8" t="s">
+      <c r="C249" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="250" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C250" s="8" t="s">
+      <c r="C250" s="6" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="251" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C251" s="8" t="s">
+      <c r="C251" s="6" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="252" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C252" s="8" t="s">
+      <c r="C252" s="6" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="253" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C253" s="8" t="s">
+      <c r="C253" s="6" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="254" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C254" s="8" t="s">
+      <c r="C254" s="6" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="255" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C255" s="8" t="s">
+      <c r="C255" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="256" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C256" s="8" t="s">
+      <c r="C256" s="6" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="257" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C257" s="8" t="s">
+      <c r="C257" s="6" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="258" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C258" s="8" t="s">
+      <c r="C258" s="6" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="259" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C259" s="8" t="s">
+      <c r="C259" s="6" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="260" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C260" s="8" t="s">
+      <c r="C260" s="6" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="261" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C261" s="8" t="s">
+      <c r="C261" s="6" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="262" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C262" s="8" t="s">
+      <c r="C262" s="6" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="263" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C263" s="8" t="s">
+      <c r="C263" s="6" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="264" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C264" s="8" t="s">
+      <c r="C264" s="6" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="265" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C265" s="8" t="s">
+      <c r="C265" s="6" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="266" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C266" s="8" t="s">
+      <c r="C266" s="6" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="267" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C267" s="8" t="s">
+      <c r="C267" s="6" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="268" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C268" s="8" t="s">
+      <c r="C268" s="6" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="269" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C269" s="8" t="s">
+      <c r="C269" s="6" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="270" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C270" s="8" t="s">
+      <c r="C270" s="6" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="271" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C271" s="8" t="s">
+      <c r="C271" s="6" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="272" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C272" s="8" t="s">
+      <c r="C272" s="6" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="273" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C273" s="8" t="s">
+      <c r="C273" s="6" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="274" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C274" s="8" t="s">
+      <c r="C274" s="6" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="275" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C275" s="8" t="s">
+      <c r="C275" s="6" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="276" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C276" s="8" t="s">
+      <c r="C276" s="6" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="277" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C277" s="8" t="s">
+      <c r="C277" s="6" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="278" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C278" s="8" t="s">
+      <c r="C278" s="6" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="279" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C279" s="8" t="s">
+      <c r="C279" s="6" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="280" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C280" s="8" t="s">
+      <c r="C280" s="6" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="281" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C281" s="8" t="s">
+      <c r="C281" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="282" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C282" s="8" t="s">
+      <c r="C282" s="6" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="283" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C283" s="8" t="s">
+      <c r="C283" s="6" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="284" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C284" s="8" t="s">
+      <c r="C284" s="6" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="285" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C285" s="8" t="s">
+      <c r="C285" s="6" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="286" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C286" s="8" t="s">
+      <c r="C286" s="6" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="287" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C287" s="8" t="s">
+      <c r="C287" s="6" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="288" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C288" s="8" t="s">
+      <c r="C288" s="6" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="289" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C289" s="8" t="s">
+      <c r="C289" s="6" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="290" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C290" s="8" t="s">
+      <c r="C290" s="6" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="291" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C291" s="8" t="s">
+      <c r="C291" s="6" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="292" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C292" s="8" t="s">
+      <c r="C292" s="6" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="293" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C293" s="8" t="s">
+      <c r="C293" s="6" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="294" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C294" s="8" t="s">
+      <c r="C294" s="6" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="295" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C295" s="8" t="s">
+      <c r="C295" s="6" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="296" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C296" s="8" t="s">
+      <c r="C296" s="6" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="297" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C297" s="8" t="s">
+      <c r="C297" s="6" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="298" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C298" s="8" t="s">
+      <c r="C298" s="6" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="299" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C299" s="8" t="s">
+      <c r="C299" s="6" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="300" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C300" s="8" t="s">
+      <c r="C300" s="6" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="301" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C301" s="8" t="s">
+      <c r="C301" s="6" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="302" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C302" s="8" t="s">
+      <c r="C302" s="6" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="303" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C303" s="8" t="s">
+      <c r="C303" s="6" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="304" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C304" s="8" t="s">
+      <c r="C304" s="6" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="305" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C305" s="8" t="s">
+      <c r="C305" s="6" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="306" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C306" s="8" t="s">
+      <c r="C306" s="6" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="307" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C307" s="8" t="s">
+      <c r="C307" s="6" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="308" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C308" s="8" t="s">
+      <c r="C308" s="6" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="309" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C309" s="8" t="s">
+      <c r="C309" s="6" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="310" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C310" s="8" t="s">
+      <c r="C310" s="6" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="311" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C311" s="8" t="s">
+      <c r="C311" s="6" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="312" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C312" s="8" t="s">
+      <c r="C312" s="6" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="313" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C313" s="8" t="s">
+      <c r="C313" s="6" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="314" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C314" s="8" t="s">
+      <c r="C314" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="315" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C315" s="8" t="s">
+      <c r="C315" s="6" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="316" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C316" s="8" t="s">
+      <c r="C316" s="6" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="317" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C317" s="8" t="s">
+      <c r="C317" s="6" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="318" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C318" s="8" t="s">
+      <c r="C318" s="6" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="319" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C319" s="8" t="s">
+      <c r="C319" s="6" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="320" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C320" s="8" t="s">
+      <c r="C320" s="6" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="321" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C321" s="8" t="s">
+      <c r="C321" s="6" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="322" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C322" s="8" t="s">
+      <c r="C322" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="323" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C323" s="8" t="s">
+      <c r="C323" s="6" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="324" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C324" s="8" t="s">
+      <c r="C324" s="6" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="325" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C325" s="8" t="s">
+      <c r="C325" s="6" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="326" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C326" s="8" t="s">
+      <c r="C326" s="6" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="327" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C327" s="8" t="s">
+      <c r="C327" s="6" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="328" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C328" s="8" t="s">
+      <c r="C328" s="6" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="329" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C329" s="8" t="s">
+      <c r="C329" s="6" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="330" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C330" s="8" t="s">
+      <c r="C330" s="6" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="331" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C331" s="8" t="s">
+      <c r="C331" s="6" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="332" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C332" s="8" t="s">
+      <c r="C332" s="6" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="333" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C333" s="8" t="s">
+      <c r="C333" s="6" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="334" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C334" s="8" t="s">
+      <c r="C334" s="6" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="335" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C335" s="8" t="s">
+      <c r="C335" s="6" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="336" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C336" s="8" t="s">
+      <c r="C336" s="6" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="337" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C337" s="8" t="s">
+      <c r="C337" s="6" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="338" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C338" s="8" t="s">
+      <c r="C338" s="6" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="339" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C339" s="8" t="s">
+      <c r="C339" s="6" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="340" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C340" s="8" t="s">
+      <c r="C340" s="6" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="341" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C341" s="8" t="s">
+      <c r="C341" s="6" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="342" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C342" s="8" t="s">
+      <c r="C342" s="6" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="343" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C343" s="8" t="s">
+      <c r="C343" s="6" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="344" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C344" s="8" t="s">
+      <c r="C344" s="6" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="345" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C345" s="8" t="s">
+      <c r="C345" s="6" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="346" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C346" s="8" t="s">
+      <c r="C346" s="6" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="347" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C347" s="8" t="s">
+      <c r="C347" s="6" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="348" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C348" s="8" t="s">
+      <c r="C348" s="6" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="349" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C349" s="8" t="s">
+      <c r="C349" s="6" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="350" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C350" s="8" t="s">
+      <c r="C350" s="6" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="351" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C351" s="8" t="s">
+      <c r="C351" s="6" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="352" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C352" s="8" t="s">
+      <c r="C352" s="6" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="353" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C353" s="8" t="s">
+      <c r="C353" s="6" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="354" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C354" s="8" t="s">
+      <c r="C354" s="6" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="355" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C355" s="8" t="s">
+      <c r="C355" s="6" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="356" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C356" s="8" t="s">
+      <c r="C356" s="6" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="357" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C357" s="8" t="s">
+      <c r="C357" s="6" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="358" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C358" s="8" t="s">
+      <c r="C358" s="6" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="359" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C359" s="8" t="s">
+      <c r="C359" s="6" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="360" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C360" s="8" t="s">
+      <c r="C360" s="6" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="361" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C361" s="8" t="s">
+      <c r="C361" s="6" t="s">
         <v>565</v>
       </c>
     </row>
     <row r="362" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C362" s="8" t="s">
+      <c r="C362" s="6" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="363" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C363" s="8" t="s">
+      <c r="C363" s="6" t="s">
         <v>569</v>
       </c>
     </row>
     <row r="364" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C364" s="8" t="s">
+      <c r="C364" s="6" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="365" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C365" s="8" t="s">
+      <c r="C365" s="6" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="366" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C366" s="8" t="s">
+      <c r="C366" s="6" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="367" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C367" s="8" t="s">
+      <c r="C367" s="6" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="368" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C368" s="8" t="s">
+      <c r="C368" s="6" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="369" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C369" s="8" t="s">
+      <c r="C369" s="6" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="370" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C370" s="8" t="s">
+      <c r="C370" s="6" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="371" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C371" s="8" t="s">
+      <c r="C371" s="6" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="372" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C372" s="8" t="s">
+      <c r="C372" s="6" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="373" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C373" s="8" t="s">
+      <c r="C373" s="6" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="374" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C374" s="8" t="s">
+      <c r="C374" s="6" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="375" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C375" s="8" t="s">
+      <c r="C375" s="6" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="376" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C376" s="8" t="s">
+      <c r="C376" s="6" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="377" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C377" s="8" t="s">
+      <c r="C377" s="6" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="378" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C378" s="8" t="s">
+      <c r="C378" s="6" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="379" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C379" s="8" t="s">
+      <c r="C379" s="6" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="380" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C380" s="8" t="s">
+      <c r="C380" s="6" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="381" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C381" s="8" t="s">
+      <c r="C381" s="6" t="s">
         <v>600</v>
       </c>
     </row>
     <row r="382" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C382" s="8" t="s">
+      <c r="C382" s="6" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="383" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C383" s="8" t="s">
+      <c r="C383" s="6" t="s">
         <v>604</v>
       </c>
     </row>
     <row r="384" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C384" s="8" t="s">
+      <c r="C384" s="6" t="s">
         <v>606</v>
       </c>
     </row>
     <row r="385" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C385" s="8" t="s">
+      <c r="C385" s="6" t="s">
         <v>608</v>
       </c>
     </row>
